--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488211_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488211_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6127</v>
+        <v>3.1964</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4484</v>
+        <v>3.0567</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1643</v>
+        <v>0.1397</v>
       </c>
       <c r="G2" t="n">
         <v>0.5063</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0413</v>
+        <v>-0.4576</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0621</v>
+        <v>-0.4539</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0209</v>
+        <v>-0.0037</v>
       </c>
       <c r="V2" t="n">
         <v>3.1477</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. ARANDA SUAREZ</t>
+          <t>X. NEWSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6987</v>
+        <v>1.8501</v>
       </c>
       <c r="E3" t="n">
-        <v>1.535</v>
+        <v>3.2119</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1636</v>
+        <v>-1.3618</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6009</v>
+        <v>-0.1168</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6945</v>
+        <v>-1.3794</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0936</v>
+        <v>1.2626</v>
       </c>
       <c r="J3" t="n">
-        <v>2.114</v>
+        <v>2.1132</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0311</v>
+        <v>0.0597</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0829</v>
+        <v>2.0535</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5131</v>
+        <v>-2.23</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3366</v>
+        <v>-1.4391</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1766</v>
+        <v>-0.7907999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9264</v>
+        <v>3.1499</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7278</v>
+        <v>-0.2925</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9774</v>
+        <v>-0.2129</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7503</v>
+        <v>-0.0796</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.63</v>
+        <v>1.8888</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.63</v>
+        <v>4.091</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.2022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. NEWSON</t>
+          <t>C. ARANDA SUAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7964</v>
+        <v>1.6931</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3306</v>
+        <v>0.8495</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5342</v>
+        <v>0.8436</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1168</v>
+        <v>1.6009</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3794</v>
+        <v>1.6945</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2626</v>
+        <v>-0.0936</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1132</v>
+        <v>2.114</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0597</v>
+        <v>2.0311</v>
       </c>
       <c r="L4" t="n">
-        <v>2.0535</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.23</v>
+        <v>-0.5131</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4391</v>
+        <v>-0.3366</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.1766</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1499</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3463</v>
+        <v>0.7222</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0943</v>
+        <v>0.2919</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.252</v>
+        <v>0.4303</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8888</v>
+        <v>-0.63</v>
       </c>
       <c r="W4" t="n">
-        <v>4.091</v>
+        <v>-0.63</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.2022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ARCONES DURAND</t>
+          <t>A. ELIAS GALLEGOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1635</v>
+        <v>-0.1625</v>
       </c>
       <c r="E5" t="n">
-        <v>2.9746</v>
+        <v>-0.2321</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.8112</v>
+        <v>0.0697</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4395</v>
+        <v>-0.0804</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4513</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8908</v>
+        <v>0.4332</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2626</v>
+        <v>0.0415</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8633</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6007</v>
+        <v>0.0415</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7021</v>
+        <v>-0.1219</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.412</v>
+        <v>-0.5135999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2901</v>
+        <v>0.3917</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>0.3706</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8529</v>
+        <v>0.3706</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5654</v>
+        <v>-0.4526</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0096</v>
+        <v>-0.2736</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4442</v>
+        <v>-0.1791</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.8888</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.5177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ELIAS GALLEGOS</t>
+          <t>A. ARCONES DURAND</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2117</v>
+        <v>-1.0111</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2321</v>
+        <v>1.7015</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0204</v>
+        <v>-2.7127</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0804</v>
+        <v>-0.4395</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5135999999999999</v>
+        <v>1.4513</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4332</v>
+        <v>-1.8908</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0415</v>
+        <v>1.2626</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.8633</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0415</v>
+        <v>-0.6007</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1219</v>
+        <v>-1.7021</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.412</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3917</v>
+        <v>-1.2901</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3706</v>
+        <v>0.9264</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5019</v>
+        <v>0.3908</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2736</v>
+        <v>0.7365</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2283</v>
+        <v>-0.3457</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.8888</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.5177</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.778</v>
+        <v>-1.6068</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9731</v>
+        <v>-0.7772</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8048999999999999</v>
+        <v>-0.8296</v>
       </c>
       <c r="G7" t="n">
         <v>-3.6779</v>
@@ -1000,13 +1000,13 @@
         <v>2.2234</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3236</v>
+        <v>-0.1523</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.332</v>
+        <v>-0.1361</v>
       </c>
       <c r="U7" t="n">
-        <v>0.008399999999999999</v>
+        <v>-0.0162</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. MERINO LUQUE</t>
+          <t>R. SANAHUJA TRESERRAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7124</v>
+        <v>-1.781</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4594</v>
+        <v>-2.3212</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.253</v>
+        <v>0.5402</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8743</v>
+        <v>-2.3593</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3903</v>
+        <v>-2.2887</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.516</v>
+        <v>-0.0706</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3047</v>
+        <v>-0.7671</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7917</v>
+        <v>-0.3737</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.487</v>
+        <v>-0.3934</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4304</v>
+        <v>-1.5922</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4014</v>
+        <v>-1.915</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.029</v>
+        <v>0.3227</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1853</v>
+        <v>1.8529</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.7793</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>2.594</v>
+        <v>2.7793</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5693</v>
+        <v>-0.6451</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9849</v>
+        <v>-0.6277</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4156</v>
+        <v>-0.0174</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.8321</v>
+        <v>-0.6294</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.8321</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. SANAHUJA TRESERRAS</t>
+          <t>R. MERINO LUQUE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7619</v>
+        <v>-2.8864</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0067</v>
+        <v>-0.1657</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2447</v>
+        <v>-2.7208</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3593</v>
+        <v>0.8743</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2887</v>
+        <v>2.3903</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0706</v>
+        <v>-1.516</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7671</v>
+        <v>3.3047</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3737</v>
+        <v>3.7917</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.3934</v>
+        <v>-0.487</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5922</v>
+        <v>-2.4304</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.915</v>
+        <v>-1.4014</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3227</v>
+        <v>-1.029</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8529</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7793</v>
+        <v>2.594</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.626</v>
+        <v>-0.7433</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.3132</v>
+        <v>-0.6911</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3129</v>
+        <v>-0.0522</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6294</v>
+        <v>-2.8321</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6294</v>
+        <v>-2.8321</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.3123</v>
+        <v>-3.7969</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3157</v>
+        <v>-3.0219</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9966</v>
+        <v>-0.775</v>
       </c>
       <c r="G10" t="n">
         <v>-1.4155</v>
@@ -1234,13 +1234,13 @@
         <v>3.7057</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6206</v>
+        <v>-1.1052</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2584</v>
+        <v>-0.9647</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3621</v>
+        <v>-0.1405</v>
       </c>
       <c r="V10" t="n">
         <v>-2.2027</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.504999999999999</v>
+        <v>-4.5051</v>
       </c>
       <c r="E11" t="n">
-        <v>2.301599999999998</v>
+        <v>2.301499999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.8069</v>
+        <v>-6.8067</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.107900000000001</v>
+        <v>-5.1079</v>
       </c>
       <c r="H11" t="n">
         <v>-5.8758</v>
@@ -1303,7 +1303,7 @@
         <v>-4.069299999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>6.484999999999999</v>
+        <v>6.485</v>
       </c>
       <c r="Q11" t="n">
         <v>-13.8964</v>
@@ -1312,13 +1312,13 @@
         <v>20.3815</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.7358</v>
+        <v>-2.7356</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3315</v>
+        <v>-2.3316</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4042999999999999</v>
+        <v>-0.4041</v>
       </c>
       <c r="V11" t="n">
         <v>-3.1465</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.1853</v>
+        <v>4.3285</v>
       </c>
       <c r="E12" t="n">
-        <v>5.4599</v>
+        <v>4.5786</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2747</v>
+        <v>-0.25</v>
       </c>
       <c r="G12" t="n">
         <v>4.5606</v>
@@ -1390,13 +1390,13 @@
         <v>1.8529</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8481</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2473</v>
+        <v>0.3659</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6009</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.6294</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1508</v>
+        <v>3.6421</v>
       </c>
       <c r="E13" t="n">
-        <v>2.9023</v>
+        <v>3.0982</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2485</v>
+        <v>0.5439000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>1.0875</v>
@@ -1468,13 +1468,13 @@
         <v>1.6676</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0453</v>
+        <v>0.5366</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0584</v>
+        <v>0.1374</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1037</v>
+        <v>0.3991</v>
       </c>
       <c r="V13" t="n">
         <v>2.2033</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0395</v>
+        <v>1.9433</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4638</v>
+        <v>5.072</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.4242</v>
+        <v>-3.1288</v>
       </c>
       <c r="G14" t="n">
         <v>4.5751</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0563</v>
+        <v>0.96</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7039</v>
+        <v>0.3121</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3524</v>
+        <v>0.6479</v>
       </c>
       <c r="V14" t="n">
         <v>-3.7771</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>A. MEJIA BERIGUETE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3221</v>
+        <v>0.3479</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3221</v>
+        <v>0.6685</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.3206</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3221</v>
+        <v>0.5963000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3221</v>
+        <v>-1.7015</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.2978</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3221</v>
+        <v>1.6841</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3221</v>
+        <v>-0.8978</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.5819</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.0878</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.8037</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.2841</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.2484</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.0892</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.1592</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. MEJIA BERIGUETE</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.3221</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3747</v>
+        <v>0.3221</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.296</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5963000000000001</v>
+        <v>0.3221</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.7015</v>
+        <v>0.3221</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2978</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6841</v>
+        <v>0.3221</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8978</v>
+        <v>0.3221</v>
       </c>
       <c r="L17" t="n">
-        <v>2.5819</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0878</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8037</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2841</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9264</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5175999999999999</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.383</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1346</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5843</v>
+        <v>-0.6571</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6274</v>
+        <v>-0.8232</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0431</v>
+        <v>0.1662</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1956</v>
@@ -1858,13 +1858,13 @@
         <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0186</v>
+        <v>-0.0914</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1604</v>
+        <v>-0.0354</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1791</v>
+        <v>-0.056</v>
       </c>
       <c r="V18" t="n">
         <v>0.63</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. DIAZ FERREIRA</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8604000000000001</v>
+        <v>-0.8268</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8855</v>
+        <v>-0.8756</v>
       </c>
       <c r="F19" t="n">
-        <v>2.0251</v>
+        <v>0.0488</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6579</v>
+        <v>0.8393</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8623</v>
+        <v>2.1019</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2045</v>
+        <v>-1.2626</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2468</v>
+        <v>2.01</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4126</v>
+        <v>2.5893</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1659</v>
+        <v>-0.5793</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4111</v>
+        <v>-1.1707</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4497</v>
+        <v>-0.4874</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0386</v>
+        <v>-0.6833</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.1499</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.6322</v>
+        <v>-3.7057</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4823</v>
+        <v>1.8529</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3741</v>
+        <v>0.5018</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1057</v>
+        <v>-0.1237</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2684</v>
+        <v>0.6254999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5733</v>
+        <v>-0.315</v>
       </c>
       <c r="W19" t="n">
-        <v>1.8877</v>
+        <v>0.9439</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>A. DIAZ FERREIRA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.439</v>
+        <v>-1.5738</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4632</v>
+        <v>-2.9834</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0242</v>
+        <v>1.4096</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8393</v>
+        <v>-0.6579</v>
       </c>
       <c r="H20" t="n">
-        <v>2.1019</v>
+        <v>-0.8623</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2626</v>
+        <v>0.2045</v>
       </c>
       <c r="J20" t="n">
-        <v>2.01</v>
+        <v>-0.2468</v>
       </c>
       <c r="K20" t="n">
-        <v>2.5893</v>
+        <v>-0.4126</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.5793</v>
+        <v>0.1659</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.1707</v>
+        <v>-0.4111</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4874</v>
+        <v>-0.4497</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6833</v>
+        <v>0.0386</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8529</v>
+        <v>-3.1499</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.7057</v>
+        <v>-4.6322</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8529</v>
+        <v>1.4823</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1104</v>
+        <v>0.6606</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7113</v>
+        <v>0.0078</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6009</v>
+        <v>0.6528</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.315</v>
+        <v>1.5733</v>
       </c>
       <c r="W20" t="n">
-        <v>0.9439</v>
+        <v>1.8877</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.8708</v>
+        <v>-1.676</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3399</v>
+        <v>-1.9482</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4691</v>
+        <v>0.2722</v>
       </c>
       <c r="G21" t="n">
         <v>0.1971</v>
@@ -2092,13 +2092,13 @@
         <v>1.297</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2706</v>
+        <v>-0.0759</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4377</v>
+        <v>-0.046</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1671</v>
+        <v>-0.0299</v>
       </c>
       <c r="V21" t="n">
         <v>-0.315</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.058</v>
+        <v>-2.8862</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2654</v>
+        <v>-2.1675</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7926</v>
+        <v>-0.7187</v>
       </c>
       <c r="G22" t="n">
         <v>-3.019</v>
@@ -2170,13 +2170,13 @@
         <v>0.3706</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4096</v>
+        <v>-0.2378</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3283</v>
+        <v>-0.2304</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0813</v>
+        <v>-0.0075</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.505199999999999</v>
+        <v>4.505299999999998</v>
       </c>
       <c r="E23" t="n">
-        <v>6.806799999999999</v>
+        <v>6.806900000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3016</v>
+        <v>-2.3015</v>
       </c>
       <c r="G23" t="n">
-        <v>5.107899999999999</v>
+        <v>5.107900000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>5.8757</v>
+        <v>5.875700000000002</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7676999999999998</v>
+        <v>-0.7677</v>
       </c>
       <c r="J23" t="n">
         <v>16.4004</v>
@@ -2236,7 +2236,7 @@
         <v>-6.4555</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.837</v>
+        <v>-4.837000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-6.485100000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.8966</v>
       </c>
       <c r="S23" t="n">
-        <v>2.7359</v>
+        <v>2.7358</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4042999999999999</v>
+        <v>0.4042000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>2.3315</v>
+        <v>2.3313</v>
       </c>
       <c r="V23" t="n">
         <v>3.1466</v>
